--- a/ig/nr-update-location-identifier/StructureDefinition-fr-core-appointment-operator.xlsx
+++ b/ig/nr-update-location-identifier/StructureDefinition-fr-core-appointment-operator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-20T15:16:44+00:00</t>
+    <t>2023-12-20T16:57:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
